--- a/candidate_v1.14/final_v1.14_status_report.xlsx
+++ b/candidate_v1.14/final_v1.14_status_report.xlsx
@@ -8,13 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="executive_summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="corrected_mapping_audit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="corrected_mapping" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="mfa_results" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="qualitative_tests" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="evidence_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="blockers" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="next_actions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="release_readiness" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="calvin_investigation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="blockers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="next_actions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="release_readiness" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,127 +442,182 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>detail</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MFA_panel_substrates</t>
+          <t>baseline_audit</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>CONDITIONAL_PASS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8/8 metrics match; 46 imbalanced (known)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>qualitative_tests_PASS</t>
+          <t>reaction_mapping</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>CORRECTED</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RuBisCO=rxn00018; epimerase=rxn01116</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>qualitative_tests_FAIL</t>
+          <t>MFA_qualitative_tests</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15/15 PASS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>With corrected mappings and ICL constraint</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>qualitative_tests_INFO</t>
+          <t>Calvin_cycle_status</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ZERO_FLUX</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Model uses proline cycling for redox balance instead of CBB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>reaction_mappings_verified</t>
+          <t>Calvin_cycle_root_cause</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>ARCHITECTURE_GAP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rxn00929 (proline cycle) is the electron sink; blocking it kills growth</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RuBisCO_correctly_identified</t>
+          <t>H2_validation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rxn00018_c0</t>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>No N2 exchange; hydrogenase is wrong source</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Calvin_cycle_active_at_baseline</t>
+          <t>loopless_FBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NO (zero RuBisCO/PRK flux)</t>
+          <t>TESTED</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Eliminates rxn00501 loop but rxn00929 persists (not a simple loop)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>glyoxylate_shunt_on_succinate</t>
+          <t>ICL_constraint</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BLOCKED (ICL constraint)</t>
+          <t>VALIDATED</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ICL=0 on succinate; -0.28% growth; 15/15 tests pass</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N2_exchange_available</t>
+          <t>recommended_model</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NO (architecture gap)</t>
+          <t>v1.13_baseline</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>With ICL constraint for succinate simulations</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H2_via_nitrogenase</t>
+          <t>next_priority</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IMPOSSIBLE (no N2)</t>
+          <t>v1.15_needed</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fix redox architecture: Calvin cycle must be the electron sink</t>
         </is>
       </c>
     </row>
@@ -578,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,25 +643,10 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>expected_role</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>model_name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>bounds</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>correct_id</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -621,25 +660,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RuBisCO_carboxylase</t>
+          <t>RuBisCO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3-phospho-D-glycerate carboxy-lyase (dimerizing; D-ribulose-1,5-bisphosphate-forming)_c0</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>[0.0,1000.0]</t>
-        </is>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>VERIFIED_CORRECT</t>
         </is>
       </c>
     </row>
@@ -651,25 +677,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>phosphoribulokinase</t>
+          <t>PRK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ATP:D-ribulose-5-phosphate 1-phosphotransferase_c0</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>[0.0,1000.0]</t>
-        </is>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>VERIFIED_CORRECT</t>
         </is>
       </c>
     </row>
@@ -686,108 +699,56 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>D-Ribulose-5-phosphate 3-epimerase_c0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>[-1000.0,1000.0]</t>
-        </is>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>CORRECTED</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rxn00336_c0</t>
+          <t>rxn05040_c0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>isocitrate_lyase</t>
+          <t>DHBP_synthase_NOT_RuBisCO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>isocitrate glyoxylate-lyase (succinate-forming)_c0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>[0.0,1000.0]</t>
-        </is>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>CORRECTED</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rxn00330_c0</t>
+          <t>rxn02507_c0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>malate_synthase</t>
+          <t>indole3GP_synthase_NOT_RuBisCO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>acetyl-CoA:glyoxylate C-acetyltransferase (thioester-hydrolysing, carboxymethyl-forming)_c0</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>[0.0,1000.0]</t>
-        </is>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>CORRECTED</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rxn13974_c0</t>
+          <t>rxn00336_c0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyruvate_Fd_oxidoreductase</t>
+          <t>ICL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>pyruvate:ferredoxin 2-oxidoreductase (CoA-acetylating)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>[-1000.0,1000.0]</t>
-        </is>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -796,28 +757,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rxn06874_c0</t>
+          <t>rxn00330_c0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nitrogenase_Mo</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>reduced ferredoxin:dinitrogen oxidoreductase (ATP-hydrolysing)_c0</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>[0.0,1000.0]</t>
-        </is>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -826,30 +774,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>rxn06874_c0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>nitrogenase</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VERIFIED_BUT_NONFUNCTIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>rxn05759_c0</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>hydrogenase_Fd</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>hydrogen:ferredoxin oxidoreductase_c0</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>[-1000.0,1000.0]</t>
-        </is>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>hydrogenase</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SHOULD_BE_BLOCKED_FOR_CGA009</t>
         </is>
       </c>
     </row>
@@ -864,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,87 +827,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>growth</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>growth</t>
+          <t>ICL</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RuBisCO_flux</t>
+          <t>RuBisCO</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PRK_flux</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ICL_flux</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>MS_flux</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>glyoxylate_shunt</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>CS_flux</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>IDH_flux</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>SDH_flux</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>POR_flux</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>nitrogenase_flux</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>hydrogenase_flux</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>CO2_exchange</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>H2_exchange</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>photon_uptake</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>ATP_synthase</t>
+          <t>POR</t>
         </is>
       </c>
     </row>
@@ -965,58 +852,17 @@
           <t>acetate</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
+      <c r="B2" t="n">
+        <v>10.702</v>
       </c>
       <c r="C2" t="n">
-        <v>10.70200607710491</v>
+        <v>2.39</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2.391257201048942</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.391257201048942</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.982654609025077</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>63.78743585572995</v>
-      </c>
-      <c r="L2" t="n">
-        <v>91.1970286029471</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-36.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>57.89982821010192</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="3">
@@ -1025,58 +871,17 @@
           <t>succinate</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
+      <c r="B3" t="n">
+        <v>10.561</v>
       </c>
       <c r="C3" t="n">
-        <v>10.56058117818294</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.403202989370285</v>
-      </c>
-      <c r="K3" t="n">
-        <v>60.36020742289497</v>
-      </c>
-      <c r="L3" t="n">
-        <v>91.5110645081386</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-36.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>58.55678075493184</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="4">
@@ -1085,58 +890,17 @@
           <t>butyrate</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
+      <c r="B4" t="n">
+        <v>10.813</v>
       </c>
       <c r="C4" t="n">
-        <v>10.81260113034499</v>
+        <v>2.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.415968569697965</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.415968569697965</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.003143458541394</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>60.44723465444329</v>
-      </c>
-      <c r="L4" t="n">
-        <v>89.76192713846517</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-36.6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>57.73230874774803</v>
+        <v>89.8</v>
       </c>
     </row>
   </sheetData>
@@ -1150,434 +914,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>substrate</t>
+          <t>finding</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>flux</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>expected</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>observed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
+          <t>type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>acetate</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>growth_feasible</t>
-        </is>
+          <t>rxn00929 (proline cycle) is essential electron sink</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>77.7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>10.7020</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>architecture</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>acetate</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>glyoxylate_shunt_active</t>
-        </is>
+          <t>rxn00501 (3-oxopropanoate) is Type III loop</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2.3913</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>loop_eliminated</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>acetate</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RuBisCO_flux_check</t>
-        </is>
+          <t>Calvin cycle not needed because proline cycle handles redox</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0 at default (no CO2 fixation in chemoheterotrophic)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>architecture</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>acetate</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CO2_production</t>
-        </is>
+          <t>Blocking both sinks kills growth (0.0)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.2300</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>acetate</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>nitrogenase_zero_no_N2</t>
-        </is>
-      </c>
-      <c r="C6">
-        <f>0 (no N2 exchange)</f>
-        <v/>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>succinate</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>growth_feasible</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>10.5606</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>succinate</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>glyoxylate_shunt_blocked</t>
-        </is>
-      </c>
-      <c r="C8">
-        <f>0 (ICL constraint)</f>
-        <v/>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.000000</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>succinate</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>RuBisCO_flux_check</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0 at default (no CO2 fixation in chemoheterotrophic)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>succinate</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CO2_production</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.2300</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>succinate</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nitrogenase_zero_no_N2</t>
-        </is>
-      </c>
-      <c r="C11">
-        <f>0 (no N2 exchange)</f>
-        <v/>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>butyrate</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>growth_feasible</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>10.8126</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>butyrate</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>glyoxylate_shunt_active</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.4160</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>butyrate</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>RuBisCO_flux_check</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0 at default (no CO2 fixation in chemoheterotrophic)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>butyrate</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CO2_production</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.2300</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>butyrate</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>nitrogenase_zero_no_N2</t>
-        </is>
-      </c>
-      <c r="C16">
-        <f>0 (no N2 exchange)</f>
-        <v/>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>critical</t>
         </is>
       </c>
     </row>
@@ -1592,54 +1005,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>blocker</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>used_for</t>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>blocks</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>McKinlay_Harwood_2011</t>
+          <t>No N2 exchange</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MFA validation, glyoxylate shunt</t>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>H2 via nitrogenase</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chowdhury_2022</t>
+          <t>Proline cycle as electron sink</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ME model precedent, ATP caps</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Calvin cycle activation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rey_2006</t>
+          <t>Hydrogenase wrong H2 source</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CGA009 defective hydrogenase</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CGA009 H2 biology</t>
         </is>
       </c>
     </row>
@@ -1654,57 +1087,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>blocker</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>severity</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>blocks</t>
+          <t>action</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>No N2 exchange</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>H2 yield validation via nitrogenase</t>
+          <t>Fix redox architecture: make Calvin cycle the primary electron sink</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Calvin cycle zero flux</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Photoheterotrophic CBB validation</t>
+          <t>Add N2 exchange or nitrogenase proton-reduction reaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Block hydrogenase for CGA009</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Validate Calvin cycle essentiality matches McKinlay/Harwood</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Re-run full MFA panel with Calvin cycle active</t>
         </is>
       </c>
     </row>
@@ -1719,78 +1163,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>action</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Add N2 exchange or nitrogenase proton-reduction reaction</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Investigate why RuBisCO/PRK have zero flux (CO2/light setup)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Block hydrogenase H2 production for CGA009</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Expand phenotype panel with more substrates</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
           <t>gate</t>
         </is>
       </c>
@@ -1832,43 +1210,55 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15/15 PASS</t>
+          <t>PASS (15/15)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H2_quantitative</t>
+          <t>Calvin_cycle_biology</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BLOCKED (no N2)</t>
+          <t>FAIL (architecture gap)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TFA_applied</t>
+          <t>H2_quantitative</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NOT_YET</t>
+          <t>BLOCKED</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>overall_v1.14_vs_baseline</t>
+          <t>v1.14_vs_baseline</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IMPROVED (ICL constraint validated)</t>
+          <t>MARGINAL_IMPROVEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>publication_ready</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NO — need v1.15</t>
         </is>
       </c>
     </row>
